--- a/www/download/IND.hours_worked.empe_ls.r.pc.zdW13.xlsx
+++ b/www/download/IND.hours_worked.empe_ls.r.pc.zdW13.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.35</t>
+          <t>0.513514202711263</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>50.57</t>
+          <t>0.505717363805475</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>0.497619766263762</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>48.92</t>
+          <t>0.489179641250694</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>48.03</t>
+          <t>0.480349843461828</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>47.11</t>
+          <t>0.471076654974004</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>46.13</t>
+          <t>0.461298308066698</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.77</t>
+          <t>0.457667217940064</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>45.52</t>
+          <t>0.455162421354089</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>0.443632926853369</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>43.13</t>
+          <t>0.431306632348328</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>43.13</t>
+          <t>0.431306632348328</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>43.13</t>
+          <t>0.431306632348328</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>43.13</t>
+          <t>0.431306632348328</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>43.13</t>
+          <t>0.431306632348328</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>21.94</t>
+          <t>0.219421352515125</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>0.207266265937951</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>19.94</t>
+          <t>0.199429130208006</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>0.203464147505076</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20.16</t>
+          <t>0.20155317609232</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>0.198487849356127</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>0.191104815277776</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>18.64</t>
+          <t>0.186364533545689</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>18.64</t>
+          <t>0.186413275003306</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>0.170729023274463</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>0.166483839261025</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>0.174262351174738</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>18.12</t>
+          <t>0.181181225606082</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>17.37</t>
+          <t>0.173709405475949</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>15.93</t>
+          <t>0.159281613297941</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>0.42599523831988</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>40.87</t>
+          <t>0.408702131235407</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>0.395026675033938</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>0.383502383050495</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>37.44</t>
+          <t>0.374378607555198</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>0.355598850934251</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>34.07</t>
+          <t>0.340683481901557</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>33.03</t>
+          <t>0.330251789269123</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>32.07</t>
+          <t>0.320711316893423</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>29.34</t>
+          <t>0.29336205743151</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>27.95</t>
+          <t>0.279532666837438</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>0.270241087940117</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>0.257621464017973</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>0.242035516855977</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>0.234985897104465</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>77.21</t>
+          <t>0.772116013000455</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>76.59</t>
+          <t>0.76590348846055</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>0.779003451540807</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>79.18</t>
+          <t>0.79177631195773</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>77.84</t>
+          <t>0.77844709904704</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>77.33</t>
+          <t>0.773299749062929</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>76.76</t>
+          <t>0.767618573713681</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.52</t>
+          <t>0.765186083719348</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>74.55</t>
+          <t>0.745462502400258</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>73.21</t>
+          <t>0.732069116919247</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>72.36</t>
+          <t>0.723576757378112</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>71.13</t>
+          <t>0.711331590026213</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>71.26</t>
+          <t>0.712606279997197</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>0.700525801712369</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>67.76</t>
+          <t>0.677623355762077</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>58.76</t>
+          <t>0.587610925924509</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>57.39</t>
+          <t>0.573850217214816</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>0.560089508505123</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>54.63</t>
+          <t>0.54632879979543</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>53.26</t>
+          <t>0.532568091085737</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>51.88</t>
+          <t>0.518807382376044</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>0.50504667366635</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>49.13</t>
+          <t>0.491285964956657</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>47.34</t>
+          <t>0.473431840320967</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>45.56</t>
+          <t>0.455577715685277</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>43.77</t>
+          <t>0.437723591049587</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>0.419066464913674</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>40.04</t>
+          <t>0.400409338777762</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>38.18</t>
+          <t>0.381752212641849</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>36.31</t>
+          <t>0.363095086505936</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>0.0679777902241639</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>0.0643201481103712</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>0.0601622780062691</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>0.0581315854973308</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>0.051742310168121</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>0.0489860399672107</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>0.0459413277129061</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>0.0461833104495654</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>0.0446164479085444</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>0.0425385029137838</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>0.0397956607547163</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>0.0392067640821937</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>0.035043283485602</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>0.0343247502136119</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>0.034481796579485</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>45.58</t>
+          <t>0.455793286170177</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.73</t>
+          <t>0.447348505887678</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>43.89</t>
+          <t>0.438894182886005</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>43.04</t>
+          <t>0.430435449198591</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>0.421977487184099</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>0.413525517919637</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>0.405084789271595</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>39.67</t>
+          <t>0.396660563697889</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>0.398486780853439</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>40.61</t>
+          <t>0.406057409676632</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>0.405489083073014</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>0.405475258494265</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>0.413042273292406</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>41.01</t>
+          <t>0.410059282372126</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>41.01</t>
+          <t>0.410059282372126</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>0.345536497015435</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>33.97</t>
+          <t>0.339688683911597</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>36.13</t>
+          <t>0.361308644707421</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>38.48</t>
+          <t>0.384836781662633</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>36.07</t>
+          <t>0.360665698854184</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>0.351035672067821</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>0.345511951200769</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>34.08</t>
+          <t>0.340789399241622</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>32.93</t>
+          <t>0.329276749737806</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>31.69</t>
+          <t>0.316874602824447</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>0.317530507307097</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>0.297281253420042</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>28.55</t>
+          <t>0.285494517891135</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>27.19</t>
+          <t>0.271885826169778</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>26.85</t>
+          <t>0.268489993577326</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>0.0939326109456895</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>0.0939326109456895</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>0.0939326109456895</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>0.0939326109456895</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>0.0927435051012311</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>0.0889369919012627</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>8.42</t>
+          <t>0.0842262533100811</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>0.079357409693207</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>0.0746160322201317</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>0.0687517414942476</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>0.0630258849152691</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>0.0633012519765343</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>0.0644352506392414</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>0.062992847723295</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>0.0585111096988344</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16.88</t>
+          <t>0.168821352214266</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>16.71</t>
+          <t>0.167064119055879</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>16.61</t>
+          <t>0.166108980147147</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>0.160628773157967</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>16.63</t>
+          <t>0.166329712298562</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>0.172277022479852</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>17.22</t>
+          <t>0.172222958592591</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>0.167609296213104</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>0.163316426390187</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>15.81</t>
+          <t>0.15806764273074</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>0.170757318867008</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0.169973710704741</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>16.03</t>
+          <t>0.160282877102351</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>0.153189399990559</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>14.91</t>
+          <t>0.149149784389191</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>0.271979832942032</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>26.12</t>
+          <t>0.261219529814393</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>25.27</t>
+          <t>0.252700628834487</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>24.38</t>
+          <t>0.24382380204701</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>0.236531283704567</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>0.233019680908274</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>0.226054672064205</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>0.218210674695979</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>22.68</t>
+          <t>0.226842682699457</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>22.91</t>
+          <t>0.229118176572386</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>23.41</t>
+          <t>0.234088403617508</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>0.23250709910756</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>29.62</t>
+          <t>0.296210077490528</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>27.26</t>
+          <t>0.272608417290703</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>0.287013369143499</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>63.92</t>
+          <t>0.639178169024211</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>61.07</t>
+          <t>0.610651794592476</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>59.62</t>
+          <t>0.596185455911039</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>0.573417043689538</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>0.559957673140102</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>53.42</t>
+          <t>0.534248755542699</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>52.47</t>
+          <t>0.524684170216068</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>51.55</t>
+          <t>0.515531341029768</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>50.31</t>
+          <t>0.503147977612</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>48.69</t>
+          <t>0.48694430586986</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>0.458104635013924</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>0.445964496624076</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>43.88</t>
+          <t>0.438806564268288</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>43.37</t>
+          <t>0.433728172604134</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>42.49</t>
+          <t>0.424858472464365</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>10.63</t>
+          <t>0.106263437677474</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>10.36</t>
+          <t>0.103561413008215</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>0.11381539800428</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>0.125843415043567</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>11.26</t>
+          <t>0.112614550587768</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>0.108608552658832</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>0.106360400845511</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>10.32</t>
+          <t>0.103208922493629</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>11.44</t>
+          <t>0.114442538882156</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>0.107278576676877</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>0.0973549415386524</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>0.110248387697885</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>0.099546114892692</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>0.102731975564615</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>0.0931268628396821</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>29.07</t>
+          <t>0.290720255660776</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>0.278246646334896</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>26.86</t>
+          <t>0.268576097911535</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>0.266659254205245</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>0.258942004077579</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>0.251541560006819</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>0.244133006823773</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>0.23617545780456</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>0.225978475648083</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>21.08</t>
+          <t>0.210765004269826</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>20.76</t>
+          <t>0.207648673642603</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>0.200512305098008</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>19.36</t>
+          <t>0.193621375301614</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>0.188721347736907</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>17.57</t>
+          <t>0.175687092197979</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>0.382610927309466</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>0.375049839897196</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>0.362015613866599</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>34.79</t>
+          <t>0.347891705082328</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>33.51</t>
+          <t>0.335092218624744</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>32.47</t>
+          <t>0.324660394691237</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>0.314183196285104</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>30.24</t>
+          <t>0.302408292901115</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>29.42</t>
+          <t>0.294242714697475</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>28.86</t>
+          <t>0.288633016550311</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>27.72</t>
+          <t>0.277198512667998</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>27.41</t>
+          <t>0.274144928280342</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>26.14</t>
+          <t>0.261386192730611</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>0.250020160056632</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>0.245511494176959</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>0.376992135926617</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>36.86</t>
+          <t>0.36862955371932</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>0.33312120235405</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>32.03</t>
+          <t>0.320337886351924</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>30.58</t>
+          <t>0.305763888667831</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>0.298468664574796</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>0.301465800345686</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>0.286544998431733</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>26.38</t>
+          <t>0.263829155815847</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>0.25257974127951</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>0.247898885167095</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>24.09</t>
+          <t>0.240941883098243</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>0.245316709959732</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>0.240737403190748</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>0.229962563199935</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>47.21</t>
+          <t>0.472116393848235</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>45.98</t>
+          <t>0.459757189451821</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>44.18</t>
+          <t>0.441811523032161</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>42.38</t>
+          <t>0.423796804426037</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>0.407702170530427</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>39.89</t>
+          <t>0.398861864115183</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>40.36</t>
+          <t>0.403552045242015</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>0.384521406831891</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>0.370883866440819</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>34.14</t>
+          <t>0.341398776532459</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>0.337414473371228</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>36.98</t>
+          <t>0.369846000932046</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>36.38</t>
+          <t>0.363754386059092</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>34.98</t>
+          <t>0.349800154854205</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>35.18</t>
+          <t>0.351778225574416</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>0.191178867083809</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>0.191178867083809</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>0.191178867083809</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>0.191178867083809</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>15.82</t>
+          <t>0.158235247075407</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>18.23</t>
+          <t>0.182349977044873</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>17.93</t>
+          <t>0.17930694852451</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>0.171657773696276</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>16.38</t>
+          <t>0.163757620963638</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>0.156687409463929</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>15.41</t>
+          <t>0.154134903470183</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>14.37</t>
+          <t>0.143672344520933</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>13.97</t>
+          <t>0.13973287869126</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>0.139787422548052</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>0.126873230368998</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>66.08</t>
+          <t>0.66077924620328</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>64.14</t>
+          <t>0.641447600189498</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>63.89</t>
+          <t>0.638859502165147</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.93</t>
+          <t>0.619304375472811</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>61.66</t>
+          <t>0.616558054215761</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>58.47</t>
+          <t>0.58467433560463</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>0.591404305632871</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>58.49</t>
+          <t>0.584877616192986</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>0.567670766837423</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>56.73</t>
+          <t>0.567275362494089</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>55.95</t>
+          <t>0.559519537836255</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>55.18</t>
+          <t>0.55176371317842</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>0.568767118920052</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>0.568767118920052</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>0.568767118920052</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>0.4705050697868</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>0.461486825218085</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>0.45246858064937</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>44.35</t>
+          <t>0.443450336080655</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>43.44</t>
+          <t>0.43443209151194</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>43.12</t>
+          <t>0.431188324556303</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>42.79</t>
+          <t>0.427944557600666</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>42.47</t>
+          <t>0.424700790645029</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>0.421457023689391</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>0.418213256733754</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>0.418213256733754</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>0.418213256733754</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>0.418213256733754</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>0.418213256733754</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>0.418213256733754</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>37.71</t>
+          <t>0.377117844982881</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>35.37</t>
+          <t>0.353671339566012</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>0.341997227742667</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>0.337505578087051</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>0.333014763123011</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>33.42</t>
+          <t>0.334181216450352</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>33.78</t>
+          <t>0.337830794761235</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>0.323605439168837</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>30.94</t>
+          <t>0.309371321548911</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>0.303545910061829</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>29.37</t>
+          <t>0.293719961317566</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>0.279311662732008</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>26.54</t>
+          <t>0.265393791170571</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>25.58</t>
+          <t>0.25580536131037</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>0.231853154148531</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>57.16</t>
+          <t>0.571605490571882</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>55.52</t>
+          <t>0.55517522431141</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>53.82</t>
+          <t>0.538217909385193</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>52.21</t>
+          <t>0.522119121021889</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>50.52</t>
+          <t>0.505192093271439</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>48.01</t>
+          <t>0.480078999938729</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>49.82</t>
+          <t>0.498245743141107</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>48.97</t>
+          <t>0.48970843019967</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>47.13</t>
+          <t>0.471301480224933</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>45.15</t>
+          <t>0.451500920155443</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>0.437112691848013</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>0.422225134139162</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>41.51</t>
+          <t>0.415079134459507</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>0.401969894335401</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>39.48</t>
+          <t>0.394767557585996</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>17.31</t>
+          <t>0.17307842397842</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>16.27</t>
+          <t>0.162677196016229</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>15.33</t>
+          <t>0.153345618888451</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>14.16</t>
+          <t>0.141555434327556</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>0.131098195656236</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>0.122810547918182</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>0.111527236561479</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>0.104831510062737</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>0.094936571467162</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>0.0941873823053707</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>0.094347155545908</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>0.094347155545908</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>0.094347155545908</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>0.094347155545908</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>0.094347155545908</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>0.23808561239466</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>0.224584889380456</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>0.211959848305746</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>19.17</t>
+          <t>0.191666685691717</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>0.185963703398713</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>0.176755805601743</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>16.15</t>
+          <t>0.161515261812081</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>14.27</t>
+          <t>0.142728903979596</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>13.71</t>
+          <t>0.137079267562861</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>0.123555389143104</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>0.113679566535551</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>0.113679566535551</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>0.113679566535551</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>0.113679566535551</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>0.113679566535551</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>0.0874944140355671</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>0.0852547166581675</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>9.36</t>
+          <t>0.0935934357297325</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>0.103360916436434</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>0.0926756734409259</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0.0900182495246576</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>0.0885197037627784</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>8.54</t>
+          <t>0.0854404772968434</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>0.0791858091383855</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>0.08058105492606</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>0.074642215385918</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>0.0719441850247218</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>0.0781024938882458</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>0.0619376648867707</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>0.0583326850869971</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>49.19</t>
+          <t>0.49193673929924</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>49.38</t>
+          <t>0.493804704058197</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>0.448641385357869</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>40.27</t>
+          <t>0.402746887085502</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>35.87</t>
+          <t>0.358675198148706</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>36.69</t>
+          <t>0.366933179386495</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>37.52</t>
+          <t>0.37520254181193</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>0.375281648922402</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>0.406750157565099</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>0.346796768209227</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>33.58</t>
+          <t>0.335799319939094</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>0.345631026463691</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>0.345484668891991</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>34.34</t>
+          <t>0.343429080852016</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>26.27</t>
+          <t>0.262700240425917</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>0.14246307523479</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>13.92</t>
+          <t>0.139200026822149</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>0.151398434179873</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>16.54</t>
+          <t>0.165390112938895</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>14.89</t>
+          <t>0.14888500967881</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>14.47</t>
+          <t>0.144742201179548</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>14.24</t>
+          <t>0.142365416860339</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>13.83</t>
+          <t>0.138284562574763</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>0.13650119204026</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>12.38</t>
+          <t>0.123764907254343</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>13.53</t>
+          <t>0.135253521246158</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>0.131256665785457</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>0.141044893972834</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>0.131265335092835</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>11.94</t>
+          <t>0.119396499562087</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>0.397487279570907</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>0.400724087474052</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>37.66</t>
+          <t>0.37662071917422</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>38.01</t>
+          <t>0.380123903743343</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>0.380950625560815</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>38.01</t>
+          <t>0.380100138109826</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>36.45</t>
+          <t>0.36450878966992</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>0.360471590143299</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>35.09</t>
+          <t>0.35094475091783</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>0.337536834761151</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>33.37</t>
+          <t>0.333706591238496</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>32.54</t>
+          <t>0.325445000205101</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>32.54</t>
+          <t>0.325445000205101</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>32.54</t>
+          <t>0.325445000205101</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>32.54</t>
+          <t>0.325445000205101</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>77.21</t>
+          <t>0.772116013000455</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>76.59</t>
+          <t>0.76590348846055</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>0.779003451540807</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>79.18</t>
+          <t>0.79177631195773</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>77.84</t>
+          <t>0.77844709904704</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>77.33</t>
+          <t>0.773299749062929</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>76.76</t>
+          <t>0.767618573713681</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.52</t>
+          <t>0.765186083719348</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>74.55</t>
+          <t>0.745462502400258</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>73.21</t>
+          <t>0.732069116919247</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>72.36</t>
+          <t>0.723576757378112</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>71.13</t>
+          <t>0.711331590026213</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>71.26</t>
+          <t>0.712606279997197</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>0.700525801712369</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>67.76</t>
+          <t>0.677623355762077</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>0.377474602870281</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>36.13</t>
+          <t>0.361325141568263</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>34.86</t>
+          <t>0.348627110800648</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>35.16</t>
+          <t>0.351648417175198</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>32.86</t>
+          <t>0.328573747592811</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>0.370957161242812</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>37.41</t>
+          <t>0.374058189861228</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>34.02</t>
+          <t>0.340228864438809</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>32.53</t>
+          <t>0.325271553390528</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>30.88</t>
+          <t>0.308840771098981</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>0.302323549640295</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>30.31</t>
+          <t>0.303141379307418</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>0.297393418325237</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>30.52</t>
+          <t>0.305223382419178</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>0.301652436258244</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>0.101413769512459</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>0.101413769512459</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>0.101413769512459</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>0.101413769512459</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>0.101413769512459</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>0.101413769512459</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>0.100688923283079</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>0.0919175361889144</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>0.0827460580841493</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>0.0756755496322918</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>0.070873543195748</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>0.0691905420451524</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>0.0706887598570042</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>0.0723543111258817</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>0.0697746962440506</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>77.21</t>
+          <t>0.772116013000455</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>76.59</t>
+          <t>0.76590348846055</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>0.779003451540807</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>79.18</t>
+          <t>0.79177631195773</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>77.84</t>
+          <t>0.77844709904704</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>77.33</t>
+          <t>0.773299749062929</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>76.76</t>
+          <t>0.767618573713681</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.52</t>
+          <t>0.765186083719348</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>74.55</t>
+          <t>0.745462502400258</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>73.21</t>
+          <t>0.732069116919247</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>72.36</t>
+          <t>0.723576757378112</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>71.13</t>
+          <t>0.711331590026213</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>71.26</t>
+          <t>0.712606279997197</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>0.700525801712369</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>67.76</t>
+          <t>0.677623355762077</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>77.21</t>
+          <t>0.772116013000455</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>76.59</t>
+          <t>0.76590348846055</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>0.779003451540807</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>79.18</t>
+          <t>0.79177631195773</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>77.84</t>
+          <t>0.77844709904704</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>77.33</t>
+          <t>0.773299749062929</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>76.76</t>
+          <t>0.767618573713681</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.52</t>
+          <t>0.765186083719348</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>74.55</t>
+          <t>0.745462502400258</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>73.21</t>
+          <t>0.732069116919247</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>72.36</t>
+          <t>0.723576757378112</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>71.13</t>
+          <t>0.711331590026213</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>71.26</t>
+          <t>0.712606279997197</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>0.700525801712369</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>67.76</t>
+          <t>0.677623355762077</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>0.0993127317611747</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>0.0993127317611747</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>0.0993127317611747</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>0.0993127317611747</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>0.0982472112919551</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>0.0942842026898373</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>0.0893821857948423</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>0.0842934763032626</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>0.0778561338265243</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>7.15</t>
+          <t>0.0714957271475096</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>0.0678969481973664</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>0.0678969481973664</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>0.0678969481973664</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>0.0678969481973664</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>0.0678969481973664</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>0.0914488084581614</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>0.0914488084581614</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>0.0914488084581614</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>0.0914488084581614</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>0.0749894749406389</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>0.0673808263326924</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>0.0632138732224457</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>0.0556361609536206</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>0.0534902479459647</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>0.0518683756185707</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>0.0484201040963663</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>0.0476703424980709</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>0.0468876941817977</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>0.0474726258084123</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>0.0422495187888463</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>0.183574335210072</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>0.183574335210072</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>0.183574335210072</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>0.183574335210072</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>16.69</t>
+          <t>0.166881956644733</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>16.96</t>
+          <t>0.16960741297952</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>18.59</t>
+          <t>0.185868122131091</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>17.22</t>
+          <t>0.172164871290872</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>16.36</t>
+          <t>0.163642538185132</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>0.154007844383604</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>14.73</t>
+          <t>0.147258115559636</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>0.138468127371644</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>0.139004486041112</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>13.92</t>
+          <t>0.139213195868857</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>13.23</t>
+          <t>0.132339042180419</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>28.69</t>
+          <t>0.286930214028155</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>0.279309868229031</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>26.92</t>
+          <t>0.269211139624737</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>26.06</t>
+          <t>0.26057750159266</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>0.259259754487222</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>0.227831437348049</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>0.218173046434896</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>0.212997126722102</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>0.205454911760616</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>20.04</t>
+          <t>0.200366324673888</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>0.19148206461261</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>0.186045047875261</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>18.07</t>
+          <t>0.180663727961747</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>0.171148680234264</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>0.192808381056411</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>69.19</t>
+          <t>0.691906080084166</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>67.76</t>
+          <t>0.677578244763732</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>66.37</t>
+          <t>0.663694246995282</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>65.81</t>
+          <t>0.65805117189792</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>65.12</t>
+          <t>0.651173149668033</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>63.72</t>
+          <t>0.637202483989795</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>62.62</t>
+          <t>0.626233572427138</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>0.613983381850842</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>59.54</t>
+          <t>0.595400068920242</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>60.75</t>
+          <t>0.607530749616735</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>59.68</t>
+          <t>0.596787584118751</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>0.588365096533454</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>57.27</t>
+          <t>0.572742039471832</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>56.33</t>
+          <t>0.563318945148701</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>55.39</t>
+          <t>0.553895850825571</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>0.463029063184399</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>45.13</t>
+          <t>0.451264471066023</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>0.439499878947647</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>42.77</t>
+          <t>0.427735286829271</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>0.415970694710895</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>40.42</t>
+          <t>0.404206102592519</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>39.24</t>
+          <t>0.392441510474143</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>38.07</t>
+          <t>0.380676918355767</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>0.373043476496218</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>36.54</t>
+          <t>0.365410034636669</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>35.97</t>
+          <t>0.359669650926721</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>0.346539297181535</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>34.41</t>
+          <t>0.344052240718244</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>33.07</t>
+          <t>0.330739805528323</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>30.08</t>
+          <t>0.300802303965736</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>13.69</t>
+          <t>0.136858462998387</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>0.13198113281166</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>13.79</t>
+          <t>0.137854881487988</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>12.92</t>
+          <t>0.129223654847093</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>0.132964519730495</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>12.76</t>
+          <t>0.127637135521551</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>0.12686831884663</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>13.25</t>
+          <t>0.132461714342905</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>13.63</t>
+          <t>0.13632976439593</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>12.61</t>
+          <t>0.126143728471291</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>0.123556121833281</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>0.124426454523109</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>0.117341745158735</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>0.115082496080503</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>0.10897207079981</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>37.49</t>
+          <t>0.374943787104932</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>36.68</t>
+          <t>0.36680442098431</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>36.12</t>
+          <t>0.361171820645218</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>35.69</t>
+          <t>0.356946152925361</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>34.61</t>
+          <t>0.346124961039618</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>34.03</t>
+          <t>0.340320921182273</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>0.336361751969791</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>32.87</t>
+          <t>0.32866516494533</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>32.09</t>
+          <t>0.320914557878256</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>31.06</t>
+          <t>0.310567821887355</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>0.304530000724804</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>30.04</t>
+          <t>0.300399551731444</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>0.299424682750058</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>0.293148671189482</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>0.284242557598052</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>36.87</t>
+          <t>0.368672009238672</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>0.360532643119716</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>35.49</t>
+          <t>0.354900042802103</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>35.07</t>
+          <t>0.350674375095598</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>33.99</t>
+          <t>0.339853183220075</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>33.4</t>
+          <t>0.334049143400795</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>33.01</t>
+          <t>0.330089974152722</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>32.24</t>
+          <t>0.322393387130435</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>0.314642780119956</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>30.43</t>
+          <t>0.304296044170436</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>29.83</t>
+          <t>0.298258222998717</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>0.294127774003093</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>29.32</t>
+          <t>0.29315290501293</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>28.69</t>
+          <t>0.286876893426968</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>0.277970779745175</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>hours_worked.empe_ls.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW13</t>
